--- a/第5回_帳簿レビュー/デモ帳簿_株式会社デモテック.xlsx
+++ b/第5回_帳簿レビュー/デモ帳簿_株式会社デモテック.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -550,158 +550,180 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>データ源</t>
+          <t>基準期間（前々事業年度）</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>demo（試算表: trial_balance）</t>
+          <t>2023-08-01 〜 2024-07-31</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>基準期間の課税売上高</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>48000000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>仕訳の行数</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>672</v>
+          <t>データ源</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>demo（試算表: trial_balance）</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>試算表の科目数</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>39</v>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>月次推移のある科目数</t>
+          <t>仕訳の行数</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>貸借差額</t>
+          <t>試算表の科目数</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>月次推移のある科目数</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>未処理明細（件）</t>
+          <t>貸借差額</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>未処理明細（金額）</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1284000</v>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>未処理明細（件）</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>未処理明細（金額）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1284000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>未処理明細の最古日</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>前期末残高（科目）</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>普通預金</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>現金</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>120000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>売掛金</t>
+          <t>普通預金</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3900000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>売上高</t>
+          <t>現金</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>42000000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>売掛金</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>3900000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>売上高</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>42000000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>繰越利益剰余金</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B24" s="3" t="n">
         <v>-4290000</v>
       </c>
     </row>
@@ -32651,101 +32673,117 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仮払金</t>
+          <t>現金</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>会議費</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>普通預金</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>みずほ銀行</t>
+        </is>
+      </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>58100</v>
+        <v>38050000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>51920500</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>58100</v>
+        <v>6129500</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>修繕費</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
+          <t>売掛金</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ガンマデザイン株式会社</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>800000</v>
+        <v>12240000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>4500000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>800000</v>
+        <v>8640000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>地代家賃</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
+          <t>売掛金</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>デルタ物流株式会社</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2340000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2340000</v>
+        <v>-550000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>売上高</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>売掛金</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ベータ工房合同会社</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>16320000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>53040000</v>
+        <v>13200000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-53040000</v>
+        <v>4320000</v>
       </c>
     </row>
     <row r="7">
@@ -32756,218 +32794,222 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ガンマデザイン株式会社</t>
+          <t>株式会社アルファ商事</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>900000</v>
+        <v>1800000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>12240000</v>
+        <v>24480000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4500000</v>
+        <v>19800000</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8640000</v>
+        <v>6480000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>売掛金</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>デルタ物流株式会社</t>
-        </is>
-      </c>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>550000</v>
-      </c>
       <c r="F8" s="3" t="n">
-        <v>-550000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>売掛金</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>ベータ工房合同会社</t>
-        </is>
-      </c>
+          <t>役員貸付金</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="3" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16320000</v>
+        <v>1500000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>13200000</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4320000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>売掛金</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>株式会社アルファ商事</t>
-        </is>
-      </c>
+          <t>工具器具備品</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="3" t="n">
-        <v>1800000</v>
+        <v>1450000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>24480000</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19800000</v>
+        <v>240000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6480000</v>
+        <v>1210000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>外注費</t>
+          <t>敷金</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="3" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>24777000</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>24777000</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>工具器具備品</t>
+          <t>未払金</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="n">
-        <v>1450000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>240000</v>
+        <v>480000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1210000</v>
+        <v>-480000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>広告宣伝費</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
+          <t>未払金</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>フリーランス佐藤</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4350000</v>
+        <v>9360000</v>
       </c>
       <c r="E13" s="3" t="n">
+        <v>9360000</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>4350000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>役員報酬</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr"/>
+          <t>未払金</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>合同会社コードワークス</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>7050000</v>
+        <v>6481000</v>
       </c>
       <c r="E14" s="3" t="n">
+        <v>6481000</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>7050000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>役員貸付金</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
+          <t>未払金</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>山田工務店</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="n">
+        <v>-820000</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>1500000</v>
-      </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1500000</v>
+        <v>-1620000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>支払報酬料</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
+          <t>未払金</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>株式会社テックパートナーズ</t>
+        </is>
+      </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>660000</v>
+        <v>7400000</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>660000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>支払手数料</t>
+          <t>未払費用</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -32975,123 +33017,131 @@
         <v>0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>79200</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>79200</v>
+        <v>-180000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>敷金</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
+          <t>預り金</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>源泉所得税</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
-        <v>1080000</v>
+        <v>-40000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1080000</v>
+        <v>-88000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>新聞図書費</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
+          <t>預り金</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>社会保険料</t>
+        </is>
+      </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26400</v>
+        <v>1104000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>1104000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>26400</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
+          <t>長期借入金</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>日本政策金融公庫</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
+        <v>-18300000</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>954000</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>954000</v>
+        <v>-18300000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>普通預金</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>みずほ銀行</t>
-        </is>
-      </c>
+          <t>資本金</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="3" t="n">
-        <v>20000000</v>
+        <v>-3000000</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>38050000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>51920500</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6129500</v>
+        <v>-3000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>未払費用</t>
+          <t>繰越利益剰余金</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>-4230000</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-180000</v>
+        <v>-4230000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>未払金</t>
+          <t>売上高</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -33102,112 +33152,96 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>480000</v>
+        <v>53040000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-480000</v>
+        <v>-53040000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>未払金</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>フリーランス佐藤</t>
-        </is>
-      </c>
+          <t>役員報酬</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>9360000</v>
+        <v>7050000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9360000</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0</v>
+        <v>7050000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>未払金</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>合同会社コードワークス</t>
-        </is>
-      </c>
+          <t>給料手当</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>6481000</v>
+        <v>7440000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6481000</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
+        <v>7440000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>未払金</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>山田工務店</t>
-        </is>
-      </c>
+          <t>法定福利費</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="3" t="n">
-        <v>-820000</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v>1656000</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>800000</v>
-      </c>
       <c r="F26" s="3" t="n">
-        <v>-1620000</v>
+        <v>1656000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>未払金</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>株式会社テックパートナーズ</t>
-        </is>
-      </c>
+          <t>外注費</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7400000</v>
+        <v>24777000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7400000</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
+        <v>24777000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>法定福利費</t>
+          <t>支払報酬料</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -33215,19 +33249,19 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1656000</v>
+        <v>660000</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1656000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>地代家賃</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -33235,19 +33269,19 @@
         <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>436800</v>
+        <v>2340000</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>436800</v>
+        <v>2340000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>減価償却費</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -33255,39 +33289,39 @@
         <v>0</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>240000</v>
+        <v>358000</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>240000</v>
+        <v>358000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>現金</t>
+          <t>広告宣伝費</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="3" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>200000</v>
+        <v>4350000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>160000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>租税公課</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -33295,19 +33329,19 @@
         <v>0</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>87000</v>
+        <v>954000</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>87000</v>
+        <v>954000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>給料手当</t>
+          <t>会議費</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -33315,59 +33349,59 @@
         <v>0</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>7440000</v>
+        <v>58100</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7440000</v>
+        <v>58100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>繰越利益剰余金</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="3" t="n">
-        <v>-4230000</v>
+        <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>436800</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-4230000</v>
+        <v>436800</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>資本金</t>
+          <t>新聞図書費</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="3" t="n">
-        <v>-3000000</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-3000000</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>修繕費</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
@@ -33375,43 +33409,39 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>358000</v>
+        <v>800000</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>358000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>長期借入金</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>日本政策金融公庫</t>
-        </is>
-      </c>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="3" t="n">
-        <v>-18300000</v>
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>79200</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-18300000</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>雑費</t>
+          <t>租税公課</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
@@ -33419,61 +33449,53 @@
         <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>456000</v>
+        <v>87000</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>456000</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>預り金</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>源泉所得税</t>
-        </is>
-      </c>
+          <t>減価償却費</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="3" t="n">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>48000</v>
+        <v>240000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-88000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>預り金</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>社会保険料</t>
-        </is>
-      </c>
+          <t>雑費</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="3" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1104000</v>
+        <v>456000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1104000</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-100000</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="41">
